--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/70.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/70.xlsx
@@ -426,13 +426,13 @@
         <v>-5.573819670102689</v>
       </c>
       <c r="E2">
-        <v>-4.644744654524896</v>
+        <v>-6.180966062990957</v>
       </c>
       <c r="F2">
-        <v>-4.439732989904988</v>
+        <v>-4.767452530167931</v>
       </c>
       <c r="G2">
-        <v>-10.82981194710494</v>
+        <v>-9.979091128241809</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-5.089496084738099</v>
       </c>
       <c r="E3">
-        <v>-5.586875557924683</v>
+        <v>-5.716675208406539</v>
       </c>
       <c r="F3">
-        <v>-3.958938608911322</v>
+        <v>-4.806847198742868</v>
       </c>
       <c r="G3">
-        <v>-10.7246193625946</v>
+        <v>-10.25255212142223</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-4.724585742831477</v>
       </c>
       <c r="E4">
-        <v>-4.981164988554727</v>
+        <v>-7.822845827003984</v>
       </c>
       <c r="F4">
-        <v>-3.875861642084559</v>
+        <v>-4.464610519745863</v>
       </c>
       <c r="G4">
-        <v>-11.85199254053801</v>
+        <v>-10.12673814874776</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-4.541904045753769</v>
       </c>
       <c r="E5">
-        <v>-6.234270730535245</v>
+        <v>-7.689382641049923</v>
       </c>
       <c r="F5">
-        <v>-3.769329452247529</v>
+        <v>-4.474912925134481</v>
       </c>
       <c r="G5">
-        <v>-11.56164776510731</v>
+        <v>-10.98605314383085</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-4.504643864494144</v>
       </c>
       <c r="E6">
-        <v>-6.173946928279068</v>
+        <v>-8.0845146405892</v>
       </c>
       <c r="F6">
-        <v>-3.483101178456007</v>
+        <v>-4.243458789118271</v>
       </c>
       <c r="G6">
-        <v>-11.74341326794099</v>
+        <v>-11.34725021489303</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-4.591903835269692</v>
       </c>
       <c r="E7">
-        <v>-7.608802974557436</v>
+        <v>-8.093349693378164</v>
       </c>
       <c r="F7">
-        <v>-3.053378132947139</v>
+        <v>-3.913858854850973</v>
       </c>
       <c r="G7">
-        <v>-11.81005786019206</v>
+        <v>-12.21044516934814</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-4.766152463609714</v>
       </c>
       <c r="E8">
-        <v>-7.431354720566874</v>
+        <v>-7.437477217425243</v>
       </c>
       <c r="F8">
-        <v>-3.095312575979058</v>
+        <v>-3.673656330693797</v>
       </c>
       <c r="G8">
-        <v>-11.99838155373904</v>
+        <v>-11.76004213818475</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-4.988898767822434</v>
       </c>
       <c r="E9">
-        <v>-8.815804322665862</v>
+        <v>-8.78023768780962</v>
       </c>
       <c r="F9">
-        <v>-2.917963256876698</v>
+        <v>-3.299706434048016</v>
       </c>
       <c r="G9">
-        <v>-11.40067910935133</v>
+        <v>-11.94441304035784</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-5.217758660556269</v>
       </c>
       <c r="E10">
-        <v>-8.768087792047041</v>
+        <v>-8.969500730486194</v>
       </c>
       <c r="F10">
-        <v>-2.65223873303927</v>
+        <v>-3.208862694452606</v>
       </c>
       <c r="G10">
-        <v>-12.11948793065666</v>
+        <v>-12.64490130264885</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-5.425352931456525</v>
       </c>
       <c r="E11">
-        <v>-9.224082482249406</v>
+        <v>-9.836762373117168</v>
       </c>
       <c r="F11">
-        <v>-2.40491556268763</v>
+        <v>-3.023454188888409</v>
       </c>
       <c r="G11">
-        <v>-12.64622552086456</v>
+        <v>-12.85509114948272</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-5.592812303991312</v>
       </c>
       <c r="E12">
-        <v>-9.547931772433945</v>
+        <v>-11.30555933208302</v>
       </c>
       <c r="F12">
-        <v>-2.074165026097843</v>
+        <v>-2.701515824729604</v>
       </c>
       <c r="G12">
-        <v>-12.05269436385633</v>
+        <v>-12.41239175778922</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-5.711344278932462</v>
       </c>
       <c r="E13">
-        <v>-10.13852176709229</v>
+        <v>-10.90358480831816</v>
       </c>
       <c r="F13">
-        <v>-1.93281655432115</v>
+        <v>-2.324686522991692</v>
       </c>
       <c r="G13">
-        <v>-11.35295759540273</v>
+        <v>-11.31936880036129</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-5.783820277270484</v>
       </c>
       <c r="E14">
-        <v>-10.4219725406544</v>
+        <v>-11.50896932755956</v>
       </c>
       <c r="F14">
-        <v>-1.982382746235061</v>
+        <v>-2.019183796471832</v>
       </c>
       <c r="G14">
-        <v>-11.71815380547635</v>
+        <v>-12.19923235160663</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-5.823230031312606</v>
       </c>
       <c r="E15">
-        <v>-10.0315501540831</v>
+        <v>-12.01978572409879</v>
       </c>
       <c r="F15">
-        <v>-1.355484236205228</v>
+        <v>-2.093202565748981</v>
       </c>
       <c r="G15">
-        <v>-11.18988343268377</v>
+        <v>-11.95111689507487</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-5.841321790828868</v>
       </c>
       <c r="E16">
-        <v>-11.10544153721006</v>
+        <v>-11.48792550884592</v>
       </c>
       <c r="F16">
-        <v>-1.246999584399799</v>
+        <v>-1.725325430533124</v>
       </c>
       <c r="G16">
-        <v>-11.5823254325456</v>
+        <v>-11.23842927247165</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-5.851016781799152</v>
       </c>
       <c r="E17">
-        <v>-12.94733494119387</v>
+        <v>-13.62174246126019</v>
       </c>
       <c r="F17">
-        <v>-1.023516827900729</v>
+        <v>-1.533497077597231</v>
       </c>
       <c r="G17">
-        <v>-10.66992915028584</v>
+        <v>-10.78371260047059</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-5.868574002073095</v>
       </c>
       <c r="E18">
-        <v>-13.08543528453179</v>
+        <v>-14.05671597511895</v>
       </c>
       <c r="F18">
-        <v>-0.6494940349235021</v>
+        <v>-1.006925457190058</v>
       </c>
       <c r="G18">
-        <v>-9.915829913531875</v>
+        <v>-10.11268157238802</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-5.905961658303359</v>
       </c>
       <c r="E19">
-        <v>-14.79988837299174</v>
+        <v>-14.62368092087928</v>
       </c>
       <c r="F19">
-        <v>-0.6553646747071422</v>
+        <v>-0.901924090313401</v>
       </c>
       <c r="G19">
-        <v>-9.538861403520604</v>
+        <v>-9.540539850109015</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-5.967884607430973</v>
       </c>
       <c r="E20">
-        <v>-14.16722432632813</v>
+        <v>-15.27387469042658</v>
       </c>
       <c r="F20">
-        <v>-0.4032750783197939</v>
+        <v>-0.6746946280514687</v>
       </c>
       <c r="G20">
-        <v>-9.18275926204336</v>
+        <v>-9.368053806421907</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-6.059429264410089</v>
       </c>
       <c r="E21">
-        <v>-15.28769559309799</v>
+        <v>-16.41293081452392</v>
       </c>
       <c r="F21">
-        <v>-0.2820468223896974</v>
+        <v>-0.5706036369504884</v>
       </c>
       <c r="G21">
-        <v>-7.896125669842231</v>
+        <v>-8.54305592639891</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-6.187529953231919</v>
       </c>
       <c r="E22">
-        <v>-16.29420781146483</v>
+        <v>-17.11642925161551</v>
       </c>
       <c r="F22">
-        <v>0.09565226512115396</v>
+        <v>-0.7655905547932557</v>
       </c>
       <c r="G22">
-        <v>-7.707553685379804</v>
+        <v>-7.984808563748228</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-6.352762826111166</v>
       </c>
       <c r="E23">
-        <v>-17.03463142561496</v>
+        <v>-17.40409603447877</v>
       </c>
       <c r="F23">
-        <v>0.1944822948469546</v>
+        <v>-0.4914208252842865</v>
       </c>
       <c r="G23">
-        <v>-7.487571244840773</v>
+        <v>-8.061381482071569</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-6.552437925263159</v>
       </c>
       <c r="E24">
-        <v>-17.29615985650594</v>
+        <v>-18.62974563855078</v>
       </c>
       <c r="F24">
-        <v>0.1007019928086197</v>
+        <v>-0.04974360978561806</v>
       </c>
       <c r="G24">
-        <v>-7.362455797275097</v>
+        <v>-7.488895463056482</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-6.786697782990163</v>
       </c>
       <c r="E25">
-        <v>-17.84139265550346</v>
+        <v>-19.56476230928451</v>
       </c>
       <c r="F25">
-        <v>0.2593981347347407</v>
+        <v>-0.452354190200859</v>
       </c>
       <c r="G25">
-        <v>-7.650403737735366</v>
+        <v>-6.946422849900427</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-7.048984099213324</v>
       </c>
       <c r="E26">
-        <v>-17.83361273715828</v>
+        <v>-18.69953395148298</v>
       </c>
       <c r="F26">
-        <v>0.1373729893631511</v>
+        <v>-0.189624214524551</v>
       </c>
       <c r="G26">
-        <v>-6.768646554441564</v>
+        <v>-6.961548732469357</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-7.327540608542562</v>
       </c>
       <c r="E27">
-        <v>-19.20109867562454</v>
+        <v>-19.57932588169318</v>
       </c>
       <c r="F27">
-        <v>-0.1031277470590322</v>
+        <v>-0.3145536160103556</v>
       </c>
       <c r="G27">
-        <v>-6.017513566490785</v>
+        <v>-6.745048985837639</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-7.609532326524664</v>
       </c>
       <c r="E28">
-        <v>-18.01662648570427</v>
+        <v>-18.98454704857774</v>
       </c>
       <c r="F28">
-        <v>-0.4016373959644592</v>
+        <v>-0.4096170591556269</v>
       </c>
       <c r="G28">
-        <v>-6.836426663812603</v>
+        <v>-6.742877267963877</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-7.881658151617512</v>
       </c>
       <c r="E29">
-        <v>-18.49787647544742</v>
+        <v>-18.77024154463875</v>
       </c>
       <c r="F29">
-        <v>-0.4457421615917133</v>
+        <v>-0.3786775366610654</v>
       </c>
       <c r="G29">
-        <v>-6.676653114996296</v>
+        <v>-7.305196601627864</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-8.125133505784781</v>
       </c>
       <c r="E30">
-        <v>-18.25912626881502</v>
+        <v>-18.51786515971727</v>
       </c>
       <c r="F30">
-        <v>-0.4279919048845255</v>
+        <v>-0.5882578030389515</v>
       </c>
       <c r="G30">
-        <v>-6.700108330142033</v>
+        <v>-6.310649131811092</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-8.324935867848119</v>
       </c>
       <c r="E31">
-        <v>-17.90816047627255</v>
+        <v>-18.83177444945498</v>
       </c>
       <c r="F31">
-        <v>-0.7002812403891399</v>
+        <v>-1.231831348887138</v>
       </c>
       <c r="G31">
-        <v>-5.84429258169396</v>
+        <v>-7.053015795173881</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-8.473615463292255</v>
       </c>
       <c r="E32">
-        <v>-18.78250918072553</v>
+        <v>-19.22149039408108</v>
       </c>
       <c r="F32">
-        <v>-0.8181860862992046</v>
+        <v>-1.194059452054286</v>
       </c>
       <c r="G32">
-        <v>-6.507368368845664</v>
+        <v>-6.566547680905676</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-8.561512944133387</v>
       </c>
       <c r="E33">
-        <v>-18.08665027928488</v>
+        <v>-18.92076802065371</v>
       </c>
       <c r="F33">
-        <v>-0.754260145457764</v>
+        <v>-0.959031739062399</v>
       </c>
       <c r="G33">
-        <v>-5.978028689843898</v>
+        <v>-6.467244556909697</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-8.576583370905755</v>
       </c>
       <c r="E34">
-        <v>-17.27905128170496</v>
+        <v>-18.37911271612225</v>
       </c>
       <c r="F34">
-        <v>-0.7848857167066645</v>
+        <v>-0.8654021998913737</v>
       </c>
       <c r="G34">
-        <v>-6.773364081835026</v>
+        <v>-6.130558765020279</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-8.514348464826506</v>
       </c>
       <c r="E35">
-        <v>-16.69886772031624</v>
+        <v>-18.19256222937627</v>
       </c>
       <c r="F35">
-        <v>-0.6023889225633082</v>
+        <v>-1.051600139590438</v>
       </c>
       <c r="G35">
-        <v>-6.44833472078938</v>
+        <v>-6.340900896948952</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-8.379539164978281</v>
       </c>
       <c r="E36">
-        <v>-16.60626042685939</v>
+        <v>-17.88700344570872</v>
       </c>
       <c r="F36">
-        <v>-0.6410430306801416</v>
+        <v>-1.185132136554316</v>
       </c>
       <c r="G36">
-        <v>-6.05055943206379</v>
+        <v>-7.063589677626313</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-8.177162173648428</v>
       </c>
       <c r="E37">
-        <v>-16.30991255932343</v>
+        <v>-17.56917702595438</v>
       </c>
       <c r="F37">
-        <v>-1.115800270042205</v>
+        <v>-1.419864122383403</v>
       </c>
       <c r="G37">
-        <v>-6.189589102531023</v>
+        <v>-6.299793852987822</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-7.917700754006807</v>
       </c>
       <c r="E38">
-        <v>-15.77147699981142</v>
+        <v>-17.04715718472018</v>
       </c>
       <c r="F38">
-        <v>-0.8886693835012062</v>
+        <v>-1.129710215470015</v>
       </c>
       <c r="G38">
-        <v>-5.900929394779811</v>
+        <v>-5.853836884483679</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-7.619704473304235</v>
       </c>
       <c r="E39">
-        <v>-15.05807931853907</v>
+        <v>-18.04617025013031</v>
       </c>
       <c r="F39">
-        <v>-1.017645359749686</v>
+        <v>-0.7416499084849472</v>
       </c>
       <c r="G39">
-        <v>-5.289425286038873</v>
+        <v>-6.098323983104395</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-7.297987256104709</v>
       </c>
       <c r="E40">
-        <v>-16.19501611680082</v>
+        <v>-16.63611665599196</v>
       </c>
       <c r="F40">
-        <v>-0.9640218242968632</v>
+        <v>-1.428246372132331</v>
       </c>
       <c r="G40">
-        <v>-5.987433949720967</v>
+        <v>-6.602861054925942</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-6.959838813040077</v>
       </c>
       <c r="E41">
-        <v>-15.32209841013426</v>
+        <v>-16.7751770358195</v>
       </c>
       <c r="F41">
-        <v>-0.6424189489361916</v>
+        <v>-1.360851228607966</v>
       </c>
       <c r="G41">
-        <v>-4.676471158351734</v>
+        <v>-5.69734408629679</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-6.615522693590626</v>
       </c>
       <c r="E42">
-        <v>-14.87661883657771</v>
+        <v>-16.40150547460257</v>
       </c>
       <c r="F42">
-        <v>-0.9011918135293263</v>
+        <v>-1.231597749279548</v>
       </c>
       <c r="G42">
-        <v>-5.001258849573013</v>
+        <v>-6.045822041397093</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-6.274115025417173</v>
       </c>
       <c r="E43">
-        <v>-14.79437722012441</v>
+        <v>-16.70027607573263</v>
       </c>
       <c r="F43">
-        <v>-0.8803136415091676</v>
+        <v>-0.9868201519567112</v>
       </c>
       <c r="G43">
-        <v>-5.413372111029187</v>
+        <v>-5.916445921722375</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-5.937206862351483</v>
       </c>
       <c r="E44">
-        <v>-13.80879560862102</v>
+        <v>-15.49762659114558</v>
       </c>
       <c r="F44">
-        <v>-0.9162266818901373</v>
+        <v>-1.481082130185092</v>
       </c>
       <c r="G44">
-        <v>-5.357109389589272</v>
+        <v>-5.188834359828118</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-5.605782463612416</v>
       </c>
       <c r="E45">
-        <v>-13.6294816233393</v>
+        <v>-15.35682727729909</v>
       </c>
       <c r="F45">
-        <v>-0.5863542147473182</v>
+        <v>-1.340892544404915</v>
       </c>
       <c r="G45">
-        <v>-5.149534873731429</v>
+        <v>-5.039459234550662</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-5.279736560004807</v>
       </c>
       <c r="E46">
-        <v>-13.55933103248648</v>
+        <v>-14.97322024410933</v>
       </c>
       <c r="F46">
-        <v>-0.9577129781571422</v>
+        <v>-1.550858829992506</v>
       </c>
       <c r="G46">
-        <v>-4.944360503389559</v>
+        <v>-4.964621042089898</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-4.955147578919461</v>
       </c>
       <c r="E47">
-        <v>-13.70217721658443</v>
+        <v>-14.84267339541621</v>
       </c>
       <c r="F47">
-        <v>-0.6527975641258665</v>
+        <v>-1.626197188542315</v>
       </c>
       <c r="G47">
-        <v>-4.199252708320254</v>
+        <v>-4.861106904167967</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-4.625856136893079</v>
       </c>
       <c r="E48">
-        <v>-13.89596420479467</v>
+        <v>-14.54040681235223</v>
       </c>
       <c r="F48">
-        <v>-1.151091206503673</v>
+        <v>-1.489327699312559</v>
       </c>
       <c r="G48">
-        <v>-4.361188043373703</v>
+        <v>-4.982051064354161</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-4.293011035644684</v>
       </c>
       <c r="E49">
-        <v>-12.60678463886905</v>
+        <v>-14.27529635852118</v>
       </c>
       <c r="F49">
-        <v>-1.28871533843738</v>
+        <v>-1.942527505384168</v>
       </c>
       <c r="G49">
-        <v>-5.044050961213632</v>
+        <v>-4.647242351785509</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-3.959580699458666</v>
       </c>
       <c r="E50">
-        <v>-12.9555586499918</v>
+        <v>-13.860148503868</v>
       </c>
       <c r="F50">
-        <v>-1.343309720486284</v>
+        <v>-1.844020538945459</v>
       </c>
       <c r="G50">
-        <v>-4.868529147267012</v>
+        <v>-4.838932870145928</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-3.627795867544963</v>
       </c>
       <c r="E51">
-        <v>-11.82261143733081</v>
+        <v>-14.00035005914548</v>
       </c>
       <c r="F51">
-        <v>-1.419589932773077</v>
+        <v>-1.859322969977375</v>
       </c>
       <c r="G51">
-        <v>-3.884681360633166</v>
+        <v>-4.43261306338348</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-3.30414812193826</v>
       </c>
       <c r="E52">
-        <v>-11.66889238714044</v>
+        <v>-13.29420699323341</v>
       </c>
       <c r="F52">
-        <v>-1.505012836084567</v>
+        <v>-1.863983364985524</v>
       </c>
       <c r="G52">
-        <v>-4.587116223701265</v>
+        <v>-4.899628412062927</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-2.99898898831316</v>
       </c>
       <c r="E53">
-        <v>-11.01518452176319</v>
+        <v>-12.97799723869981</v>
       </c>
       <c r="F53">
-        <v>-1.55183961699742</v>
+        <v>-1.909679424393556</v>
       </c>
       <c r="G53">
-        <v>-4.387371148043799</v>
+        <v>-4.324354913703772</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-2.721821949163048</v>
       </c>
       <c r="E54">
-        <v>-10.71525010281316</v>
+        <v>-13.39023781304007</v>
       </c>
       <c r="F54">
-        <v>-1.643768517890498</v>
+        <v>-1.724644512528023</v>
       </c>
       <c r="G54">
-        <v>-4.821496226790587</v>
+        <v>-4.851410316283442</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-2.479482356863675</v>
       </c>
       <c r="E55">
-        <v>-11.18124366362446</v>
+        <v>-12.61555629302191</v>
       </c>
       <c r="F55">
-        <v>-1.628904293214664</v>
+        <v>-1.720905262071786</v>
       </c>
       <c r="G55">
-        <v>-4.132690879707667</v>
+        <v>-4.835794472974699</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-2.279215576967797</v>
       </c>
       <c r="E56">
-        <v>-10.56866339918487</v>
+        <v>-13.10177401875147</v>
       </c>
       <c r="F56">
-        <v>-1.681734252695605</v>
+        <v>-1.624209935142999</v>
       </c>
       <c r="G56">
-        <v>-5.295427305101572</v>
+        <v>-4.269260814839221</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-2.12197965464729</v>
       </c>
       <c r="E57">
-        <v>-10.36372730796774</v>
+        <v>-12.03592067698812</v>
       </c>
       <c r="F57">
-        <v>-1.610737367703868</v>
+        <v>-2.186425376525232</v>
       </c>
       <c r="G57">
-        <v>-4.897993002566526</v>
+        <v>-4.574996316481994</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-2.002692773093532</v>
       </c>
       <c r="E58">
-        <v>-10.14795004997626</v>
+        <v>-10.70363003850947</v>
       </c>
       <c r="F58">
-        <v>-1.573749934801467</v>
+        <v>-1.708999965758751</v>
       </c>
       <c r="G58">
-        <v>-5.443796024535088</v>
+        <v>-5.416318496559137</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-1.915733442290502</v>
       </c>
       <c r="E59">
-        <v>-10.05523860161722</v>
+        <v>-11.21819601152705</v>
       </c>
       <c r="F59">
-        <v>-1.810462547090648</v>
+        <v>-1.916733801195797</v>
       </c>
       <c r="G59">
-        <v>-5.438025743660138</v>
+        <v>-6.168305605259048</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-1.856955404747817</v>
       </c>
       <c r="E60">
-        <v>-9.537475525950233</v>
+        <v>-11.48378648360291</v>
       </c>
       <c r="F60">
-        <v>-1.622969869141008</v>
+        <v>-1.931993157122767</v>
       </c>
       <c r="G60">
-        <v>-5.22416450182322</v>
+        <v>-5.247315146779344</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-1.819764516874012</v>
       </c>
       <c r="E61">
-        <v>-10.16953728557082</v>
+        <v>-11.25047497425372</v>
       </c>
       <c r="F61">
-        <v>-1.783326059342339</v>
+        <v>-1.875370931671809</v>
       </c>
       <c r="G61">
-        <v>-5.456293333945837</v>
+        <v>-5.3516238156307</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-1.797049977417319</v>
       </c>
       <c r="E62">
-        <v>-9.883731705524724</v>
+        <v>-11.14003907862867</v>
       </c>
       <c r="F62">
-        <v>-1.537557734605754</v>
+        <v>-1.99452909746231</v>
       </c>
       <c r="G62">
-        <v>-5.730383330778716</v>
+        <v>-5.837181529875605</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-1.787608436543544</v>
       </c>
       <c r="E63">
-        <v>-8.922825748889137</v>
+        <v>-11.25833187665703</v>
       </c>
       <c r="F63">
-        <v>-1.500446046592933</v>
+        <v>-2.048088848625117</v>
       </c>
       <c r="G63">
-        <v>-6.163723810232697</v>
+        <v>-5.613895164888381</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-1.790066816922001</v>
       </c>
       <c r="E64">
-        <v>-9.241806929515429</v>
+        <v>-10.63355643171478</v>
       </c>
       <c r="F64">
-        <v>-1.460696008402196</v>
+        <v>-1.966060594930299</v>
       </c>
       <c r="G64">
-        <v>-6.043713223888577</v>
+        <v>-6.108563500457361</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-1.802347897688684</v>
       </c>
       <c r="E65">
-        <v>-9.087716544456429</v>
+        <v>-11.03108399400412</v>
       </c>
       <c r="F65">
-        <v>-1.855870334642506</v>
+        <v>-2.173093631544577</v>
       </c>
       <c r="G65">
-        <v>-6.488865729826678</v>
+        <v>-5.855399461978214</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-1.822411435648641</v>
       </c>
       <c r="E66">
-        <v>-9.38201301326691</v>
+        <v>-11.62267930989217</v>
       </c>
       <c r="F66">
-        <v>-1.707553636273463</v>
+        <v>-2.270639691796038</v>
       </c>
       <c r="G66">
-        <v>-5.910152574652221</v>
+        <v>-6.258670256298995</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-1.847654450695204</v>
       </c>
       <c r="E67">
-        <v>-9.597595546876066</v>
+        <v>-11.42374344673521</v>
       </c>
       <c r="F67">
-        <v>-1.762167070772632</v>
+        <v>-1.976729138710954</v>
       </c>
       <c r="G67">
-        <v>-6.355665930054101</v>
+        <v>-5.983391773617517</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-1.871803026621549</v>
       </c>
       <c r="E68">
-        <v>-8.613322664360897</v>
+        <v>-11.46030181739913</v>
       </c>
       <c r="F68">
-        <v>-1.455641310510314</v>
+        <v>-2.420034924523526</v>
       </c>
       <c r="G68">
-        <v>-5.780018340049009</v>
+        <v>-5.96298557091345</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-1.886959729504205</v>
       </c>
       <c r="E69">
-        <v>-9.272310730431096</v>
+        <v>-11.71995546005093</v>
       </c>
       <c r="F69">
-        <v>-1.615890641316684</v>
+        <v>-2.387781611328124</v>
       </c>
       <c r="G69">
-        <v>-6.132657650892177</v>
+        <v>-6.646474181860301</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-1.887508435981694</v>
       </c>
       <c r="E70">
-        <v>-10.05440083392581</v>
+        <v>-10.59546743683627</v>
       </c>
       <c r="F70">
-        <v>-1.954814679069893</v>
+        <v>-2.381713820102618</v>
       </c>
       <c r="G70">
-        <v>-6.427137297701427</v>
+        <v>-6.166100781929894</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-1.868980161801138</v>
       </c>
       <c r="E71">
-        <v>-9.937688473326117</v>
+        <v>-11.43252868631009</v>
       </c>
       <c r="F71">
-        <v>-1.446865586245056</v>
+        <v>-2.293616118447488</v>
       </c>
       <c r="G71">
-        <v>-6.333472032758827</v>
+        <v>-5.952560663010284</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-1.826994027638365</v>
       </c>
       <c r="E72">
-        <v>-9.598786535540082</v>
+        <v>-12.15473424952736</v>
       </c>
       <c r="F72">
-        <v>-1.646348053982816</v>
+        <v>-2.469200186614482</v>
       </c>
       <c r="G72">
-        <v>-6.345426412701135</v>
+        <v>-6.168457890353855</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-1.759403071901828</v>
       </c>
       <c r="E73">
-        <v>-10.10531899566805</v>
+        <v>-12.11414553699661</v>
       </c>
       <c r="F73">
-        <v>-1.67160994629859</v>
+        <v>-2.196814760491144</v>
       </c>
       <c r="G73">
-        <v>-5.220287852996734</v>
+        <v>-6.252479536140558</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-1.664868531215033</v>
       </c>
       <c r="E74">
-        <v>-11.26137953966419</v>
+        <v>-12.01593199271826</v>
       </c>
       <c r="F74">
-        <v>-1.778041075312479</v>
+        <v>-2.781030811724329</v>
       </c>
       <c r="G74">
-        <v>-5.673610785325755</v>
+        <v>-6.008889595360984</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-1.544841877134897</v>
       </c>
       <c r="E75">
-        <v>-11.50075467570965</v>
+        <v>-11.33582312387629</v>
       </c>
       <c r="F75">
-        <v>-2.015919200537398</v>
+        <v>-2.62869735981911</v>
       </c>
       <c r="G75">
-        <v>-5.553404876794819</v>
+        <v>-6.439773650024825</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-1.403391359732632</v>
       </c>
       <c r="E76">
-        <v>-10.67775886650365</v>
+        <v>-12.46555964846584</v>
       </c>
       <c r="F76">
-        <v>-1.810861820178798</v>
+        <v>-2.826771602972111</v>
       </c>
       <c r="G76">
-        <v>-5.622605210202204</v>
+        <v>-5.870343264542485</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-1.246542198287432</v>
       </c>
       <c r="E77">
-        <v>-10.74555917934649</v>
+        <v>-13.27582591723628</v>
       </c>
       <c r="F77">
-        <v>-1.908602546769917</v>
+        <v>-2.690206124579182</v>
       </c>
       <c r="G77">
-        <v>-5.246553721305311</v>
+        <v>-5.709659315702879</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-1.083115135236361</v>
       </c>
       <c r="E78">
-        <v>-12.310971131266</v>
+        <v>-14.42633002362501</v>
       </c>
       <c r="F78">
-        <v>-2.08562714585038</v>
+        <v>-2.60217883415329</v>
       </c>
       <c r="G78">
-        <v>-5.560330538062973</v>
+        <v>-5.763531823263439</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-0.921386198886966</v>
       </c>
       <c r="E79">
-        <v>-12.29033034673904</v>
+        <v>-14.1261737094486</v>
       </c>
       <c r="F79">
-        <v>-1.850046083433423</v>
+        <v>-2.586783625972261</v>
       </c>
       <c r="G79">
-        <v>-5.278252194843833</v>
+        <v>-5.533246965006196</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-0.7695204768588167</v>
       </c>
       <c r="E80">
-        <v>-13.95267881326673</v>
+        <v>-14.95487086743025</v>
       </c>
       <c r="F80">
-        <v>-2.284051788414765</v>
+        <v>-2.87349649469442</v>
       </c>
       <c r="G80">
-        <v>-4.831050461216924</v>
+        <v>-4.902809846326166</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-0.6341027310117008</v>
       </c>
       <c r="E81">
-        <v>-13.79897334849839</v>
+        <v>-14.42531564544729</v>
       </c>
       <c r="F81">
-        <v>-2.22812870505177</v>
+        <v>-2.576467138337796</v>
       </c>
       <c r="G81">
-        <v>-5.247745517699449</v>
+        <v>-5.008866483222258</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-0.5196723555870604</v>
       </c>
       <c r="E82">
-        <v>-15.31199085614914</v>
+        <v>-15.98537946956373</v>
       </c>
       <c r="F82">
-        <v>-1.859478703049101</v>
+        <v>-2.920247894173619</v>
       </c>
       <c r="G82">
-        <v>-4.558655463700151</v>
+        <v>-5.234927085371391</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-0.4291112799459297</v>
       </c>
       <c r="E83">
-        <v>-16.59516113706659</v>
+        <v>-17.792711559921</v>
       </c>
       <c r="F83">
-        <v>-2.151670393773376</v>
+        <v>-3.244528052980138</v>
       </c>
       <c r="G83">
-        <v>-4.363942417262377</v>
+        <v>-4.069333659177095</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-0.3654862067451112</v>
       </c>
       <c r="E84">
-        <v>-17.65119674718131</v>
+        <v>-18.47179699363724</v>
       </c>
       <c r="F84">
-        <v>-2.380342043683582</v>
+        <v>-3.089218276996662</v>
       </c>
       <c r="G84">
-        <v>-4.432771969569364</v>
+        <v>-4.265615904200484</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-0.331814456701381</v>
       </c>
       <c r="E85">
-        <v>-17.26311105319796</v>
+        <v>-19.14245493722521</v>
       </c>
       <c r="F85">
-        <v>-2.40622935338847</v>
+        <v>-3.420480744641379</v>
       </c>
       <c r="G85">
-        <v>-4.542946925116309</v>
+        <v>-4.039310321681445</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-0.3306596213442948</v>
       </c>
       <c r="E86">
-        <v>-18.86242316153889</v>
+        <v>-19.11054278089316</v>
       </c>
       <c r="F86">
-        <v>-2.82143028995886</v>
+        <v>-3.197893453304735</v>
       </c>
       <c r="G86">
-        <v>-4.334303103049282</v>
+        <v>-3.94725729241647</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-0.3646730676459828</v>
       </c>
       <c r="E87">
-        <v>-20.02201138678701</v>
+        <v>-21.1478126674639</v>
       </c>
       <c r="F87">
-        <v>-2.445109605806267</v>
+        <v>-3.16712457449515</v>
       </c>
       <c r="G87">
-        <v>-4.024829995492672</v>
+        <v>-3.973152379624649</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-0.4372713371177943</v>
       </c>
       <c r="E88">
-        <v>-21.60119895663784</v>
+        <v>-22.31348716177832</v>
       </c>
       <c r="F88">
-        <v>-2.584184209062276</v>
+        <v>-3.462007630911121</v>
       </c>
       <c r="G88">
-        <v>-4.427773045805065</v>
+        <v>-4.465910530417469</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-0.5495038324374975</v>
       </c>
       <c r="E89">
-        <v>-22.73089019648732</v>
+        <v>-23.48345464945202</v>
       </c>
       <c r="F89">
-        <v>-2.702697905013399</v>
+        <v>-3.426931241606979</v>
       </c>
       <c r="G89">
-        <v>-3.990360595337781</v>
+        <v>-4.285144812336644</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-0.7006484572757308</v>
       </c>
       <c r="E90">
-        <v>-24.79052168770794</v>
+        <v>-25.87854643821284</v>
       </c>
       <c r="F90">
-        <v>-2.771398555564576</v>
+        <v>-3.595839496874812</v>
       </c>
       <c r="G90">
-        <v>-3.741255285689781</v>
+        <v>-4.498817353077825</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-0.8909524174164258</v>
       </c>
       <c r="E91">
-        <v>-26.01082316397689</v>
+        <v>-26.86143813615567</v>
       </c>
       <c r="F91">
-        <v>-2.885436582438373</v>
+        <v>-3.61507832980483</v>
       </c>
       <c r="G91">
-        <v>-4.122017680889057</v>
+        <v>-4.36869636065677</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-1.120547845466844</v>
       </c>
       <c r="E92">
-        <v>-27.40698792833372</v>
+        <v>-28.65844077730144</v>
       </c>
       <c r="F92">
-        <v>-2.583120585317082</v>
+        <v>-3.68660868340397</v>
       </c>
       <c r="G92">
-        <v>-3.791592130614399</v>
+        <v>-4.23355989174372</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-1.38747570359866</v>
       </c>
       <c r="E93">
-        <v>-29.78411073223211</v>
+        <v>-30.3622700657394</v>
       </c>
       <c r="F93">
-        <v>-2.581349535809896</v>
+        <v>-3.314863072417039</v>
       </c>
       <c r="G93">
-        <v>-4.421516114735843</v>
+        <v>-4.819655563470753</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-1.688189814009823</v>
       </c>
       <c r="E94">
-        <v>-31.90420187992913</v>
+        <v>-32.88210772798952</v>
       </c>
       <c r="F94">
-        <v>-2.453949114361541</v>
+        <v>-3.973348888250422</v>
       </c>
       <c r="G94">
-        <v>-5.252072400719277</v>
+        <v>-4.915558757197899</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-2.020494111296559</v>
       </c>
       <c r="E95">
-        <v>-34.17000347153396</v>
+        <v>-34.44631737005999</v>
       </c>
       <c r="F95">
-        <v>-2.663659434421667</v>
+        <v>-3.8919112605138</v>
       </c>
       <c r="G95">
-        <v>-4.78537155386606</v>
+        <v>-4.878166145331831</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-2.379088412073827</v>
       </c>
       <c r="E96">
-        <v>-37.17129716909457</v>
+        <v>-37.23564452050657</v>
       </c>
       <c r="F96">
-        <v>-2.792276727584734</v>
+        <v>-3.753149780136049</v>
       </c>
       <c r="G96">
-        <v>-5.439661153156539</v>
+        <v>-5.158191950316624</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-2.75143063177772</v>
       </c>
       <c r="E97">
-        <v>-37.69553369835553</v>
+        <v>-38.63774385005045</v>
       </c>
       <c r="F97">
-        <v>-2.563368164597327</v>
+        <v>-3.774412314631107</v>
       </c>
       <c r="G97">
-        <v>-5.982570758323778</v>
+        <v>-5.325050066586971</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-3.128474138719102</v>
       </c>
       <c r="E98">
-        <v>-40.78423373697519</v>
+        <v>-41.36444899768196</v>
       </c>
       <c r="F98">
-        <v>-2.696772592981174</v>
+        <v>-3.524530317372219</v>
       </c>
       <c r="G98">
-        <v>-5.875213077030753</v>
+        <v>-6.162386349834832</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-3.489383687270208</v>
       </c>
       <c r="E99">
-        <v>-44.1053984603046</v>
+        <v>-43.64890110948738</v>
       </c>
       <c r="F99">
-        <v>-2.304382409581673</v>
+        <v>-3.887129095497438</v>
       </c>
       <c r="G99">
-        <v>-5.87876860293993</v>
+        <v>-5.795945374638444</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-3.824863321686056</v>
       </c>
       <c r="E100">
-        <v>-45.96593106330398</v>
+        <v>-46.60499610797743</v>
       </c>
       <c r="F100">
-        <v>-2.304836354918407</v>
+        <v>-3.587089451999041</v>
       </c>
       <c r="G100">
-        <v>-7.068356863202863</v>
+        <v>-6.996541198819453</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-4.102649311866371</v>
       </c>
       <c r="E101">
-        <v>-47.32544009480572</v>
+        <v>-48.62849264085384</v>
       </c>
       <c r="F101">
-        <v>-2.007889835302063</v>
+        <v>-3.662012798480047</v>
       </c>
       <c r="G101">
-        <v>-7.038310351888438</v>
+        <v>-7.357963386978307</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-4.333144797022186</v>
       </c>
       <c r="E102">
-        <v>-50.05289923335951</v>
+        <v>-50.29029542626361</v>
       </c>
       <c r="F102">
-        <v>-1.94675052240364</v>
+        <v>-3.51804751407791</v>
       </c>
       <c r="G102">
-        <v>-7.714608457923991</v>
+        <v>-7.700422770288214</v>
       </c>
     </row>
   </sheetData>
